--- a/output/fama_macbeth.xlsx
+++ b/output/fama_macbeth.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="16">
   <si>
     <t>Spec</t>
   </si>
@@ -28,6 +28,9 @@
     <t>t-stat</t>
   </si>
   <si>
+    <t>p-value</t>
+  </si>
+  <si>
     <t>T</t>
   </si>
   <si>
@@ -49,13 +52,13 @@
     <t>ADJ_RRR_PCT</t>
   </si>
   <si>
-    <t>SIZE_LAG</t>
-  </si>
-  <si>
-    <t>BTM_LAG</t>
-  </si>
-  <si>
-    <t>PM_LAG</t>
+    <t>SIZE</t>
+  </si>
+  <si>
+    <t>BTM</t>
+  </si>
+  <si>
+    <t>PM_OPER_PCT</t>
   </si>
   <si>
     <t>RRR_PCT</t>
@@ -416,10 +419,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -438,205 +441,238 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2">
+        <v>0.0002879402625832684</v>
+      </c>
+      <c r="D2">
+        <v>1.75442180372473</v>
+      </c>
+      <c r="E2">
+        <v>0.09029795305654888</v>
+      </c>
+      <c r="F2">
+        <v>29</v>
+      </c>
+      <c r="G2">
+        <v>112.0344827586207</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3">
+        <v>0.0002997821144740685</v>
+      </c>
+      <c r="D3">
+        <v>1.90177880784809</v>
+      </c>
+      <c r="E3">
+        <v>0.06753466141003894</v>
+      </c>
+      <c r="F3">
+        <v>29</v>
+      </c>
+      <c r="G3">
+        <v>109.8965517241379</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4">
+        <v>-0.01075316485908062</v>
+      </c>
+      <c r="D4">
+        <v>-1.318335677206054</v>
+      </c>
+      <c r="E4">
+        <v>0.1980744869400726</v>
+      </c>
+      <c r="F4">
+        <v>29</v>
+      </c>
+      <c r="G4">
+        <v>109.8965517241379</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5">
+        <v>-0.02731271136806348</v>
+      </c>
+      <c r="D5">
+        <v>-1.839842940887378</v>
+      </c>
+      <c r="E5">
+        <v>0.07641569268920986</v>
+      </c>
+      <c r="F5">
+        <v>29</v>
+      </c>
+      <c r="G5">
+        <v>109.8965517241379</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6">
+        <v>0.000329034106573682</v>
+      </c>
+      <c r="D6">
+        <v>0.7378666591303339</v>
+      </c>
+      <c r="E6">
+        <v>0.466734892260563</v>
+      </c>
+      <c r="F6">
+        <v>29</v>
+      </c>
+      <c r="G6">
+        <v>109.8965517241379</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>0.0002363926866202096</v>
+      </c>
+      <c r="D7">
+        <v>1.61199398310648</v>
+      </c>
+      <c r="E7">
+        <v>0.1181796620495035</v>
+      </c>
+      <c r="F7">
+        <v>29</v>
+      </c>
+      <c r="G7">
+        <v>112.0344827586207</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="C2">
-        <v>0.0006741313481905914</v>
-      </c>
-      <c r="D2">
-        <v>2.926724575978036</v>
-      </c>
-      <c r="E2">
-        <v>30</v>
-      </c>
-      <c r="F2">
-        <v>111.9666666666667</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8">
+        <v>0.0002424659597090824</v>
+      </c>
+      <c r="D8">
+        <v>1.716677220002964</v>
+      </c>
+      <c r="E8">
+        <v>0.0970829437430919</v>
+      </c>
+      <c r="F8">
+        <v>29</v>
+      </c>
+      <c r="G8">
+        <v>109.8965517241379</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
         <v>10</v>
       </c>
-      <c r="C3">
-        <v>0.0006352060485010741</v>
-      </c>
-      <c r="D3">
-        <v>3.486244187216763</v>
-      </c>
-      <c r="E3">
-        <v>30</v>
-      </c>
-      <c r="F3">
-        <v>109.3666666666667</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4">
-        <v>-0.01363834767206318</v>
-      </c>
-      <c r="D4">
-        <v>-1.308771720441515</v>
-      </c>
-      <c r="E4">
-        <v>30</v>
-      </c>
-      <c r="F4">
-        <v>109.3666666666667</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="B9" t="s">
         <v>12</v>
       </c>
-      <c r="C5">
-        <v>-0.05124747287930022</v>
-      </c>
-      <c r="D5">
-        <v>-2.243982937669736</v>
-      </c>
-      <c r="E5">
-        <v>30</v>
-      </c>
-      <c r="F5">
-        <v>109.3666666666667</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C9">
+        <v>-0.01064255057211191</v>
+      </c>
+      <c r="D9">
+        <v>-1.318912014615417</v>
+      </c>
+      <c r="E9">
+        <v>0.1978842266131732</v>
+      </c>
+      <c r="F9">
+        <v>29</v>
+      </c>
+      <c r="G9">
+        <v>109.8965517241379</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
         <v>13</v>
       </c>
-      <c r="C6">
-        <v>7.227146182597983E-05</v>
-      </c>
-      <c r="D6">
-        <v>0.187872942400116</v>
-      </c>
-      <c r="E6">
-        <v>30</v>
-      </c>
-      <c r="F6">
-        <v>109.3666666666667</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C10">
+        <v>-0.02832703837097514</v>
+      </c>
+      <c r="D10">
+        <v>-1.886606596673551</v>
+      </c>
+      <c r="E10">
+        <v>0.0696232318835778</v>
+      </c>
+      <c r="F10">
+        <v>29</v>
+      </c>
+      <c r="G10">
+        <v>109.8965517241379</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
         <v>14</v>
       </c>
-      <c r="C7">
-        <v>0.000620227798643201</v>
-      </c>
-      <c r="D7">
-        <v>2.853872912935563</v>
-      </c>
-      <c r="E7">
-        <v>30</v>
-      </c>
-      <c r="F7">
-        <v>111.9666666666667</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8">
-        <v>0.0006065296471276596</v>
-      </c>
-      <c r="D8">
-        <v>3.489891091437128</v>
-      </c>
-      <c r="E8">
-        <v>30</v>
-      </c>
-      <c r="F8">
-        <v>109.3666666666667</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9">
-        <v>-0.0135659386605565</v>
-      </c>
-      <c r="D9">
-        <v>-1.324345358885211</v>
-      </c>
-      <c r="E9">
-        <v>30</v>
-      </c>
-      <c r="F9">
-        <v>109.3666666666667</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10">
-        <v>-0.05115551310830751</v>
-      </c>
-      <c r="D10">
-        <v>-2.226878517042222</v>
-      </c>
-      <c r="E10">
-        <v>30</v>
-      </c>
-      <c r="F10">
-        <v>109.3666666666667</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>13</v>
-      </c>
       <c r="C11">
-        <v>8.892994905721056E-05</v>
+        <v>0.0003174979635714583</v>
       </c>
       <c r="D11">
-        <v>0.2287340879391966</v>
+        <v>0.7151915153068801</v>
       </c>
       <c r="E11">
-        <v>30</v>
+        <v>0.4804122064792588</v>
       </c>
       <c r="F11">
-        <v>109.3666666666667</v>
+        <v>29</v>
+      </c>
+      <c r="G11">
+        <v>109.8965517241379</v>
       </c>
     </row>
   </sheetData>
